--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
@@ -90,12 +90,12 @@
     <t xml:space="preserve">Quirihue</t>
   </si>
   <si>
+    <t xml:space="preserve">Coelemu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Portezuelo</t>
   </si>
   <si>
-    <t xml:space="preserve">Coelemu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chillán</t>
   </si>
   <si>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:44</t>
+    <t xml:space="preserve">2026-09-09 22:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -838,7 +838,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>16205</v>
+        <v>16203</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2024</v>
@@ -855,7 +855,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>16203</v>
+        <v>16205</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:31</t>
+    <t xml:space="preserve">2026-09-12 19:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
@@ -72,12 +72,12 @@
     <t xml:space="preserve">El Carmen</t>
   </si>
   <si>
+    <t xml:space="preserve">Pemuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ranquil</t>
   </si>
   <si>
-    <t xml:space="preserve">Pemuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ninhue</t>
   </si>
   <si>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:48</t>
+    <t xml:space="preserve">2026-09-24 00:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -736,7 +736,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>16206</v>
+        <v>16105</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2024</v>
@@ -753,7 +753,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>16105</v>
+        <v>16206</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:26</t>
+    <t xml:space="preserve">2026-09-27 22:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:14</t>
+    <t xml:space="preserve">2026-10-01 20:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:55</t>
+    <t xml:space="preserve">2026-10-02 13:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Pemuco</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Ninhue</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:21</t>
+    <t xml:space="preserve">2026-10-04 08:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:11</t>
+    <t xml:space="preserve">2026-10-05 08:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
